--- a/All_in_One_PM_Workbook.xlsx
+++ b/All_in_One_PM_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lalith Gali\Desktop\1\DASHBOARD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25174FD-B1CA-4293-A119-E45DA6957D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC89305D-56F1-448A-A3A3-F20A6C03BD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="604" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="604" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RAID Dashboard" sheetId="3" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="508">
   <si>
     <t>RACI MATRIX</t>
   </si>
@@ -1604,7 +1604,10 @@
     <t>sss</t>
   </si>
   <si>
-    <t>sssssssssssss</t>
+    <t>INDIA</t>
+  </si>
+  <si>
+    <t>asdf</t>
   </si>
 </sst>
 </file>
@@ -1869,7 +1872,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1993,6 +1996,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3139,7 +3148,7 @@
     <xf numFmtId="9" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3593,6 +3602,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="23" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -7261,7 +7279,7 @@
     <row r="9" spans="1:23" ht="17.399999999999999" customHeight="1">
       <c r="A9" s="79"/>
       <c r="B9" s="79"/>
-      <c r="C9" s="82"/>
+      <c r="C9" s="207"/>
       <c r="D9" s="80"/>
       <c r="E9" s="80"/>
       <c r="F9" s="80"/>
@@ -8340,13 +8358,14 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="13.5" customHeight="1">
-      <c r="A2" s="57" t="str">
-        <f t="shared" ref="A2:A11" si="0">IF(COUNTA($D2:$N2)=0,"","CR-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
+      <c r="A2" s="57">
+        <v>1</v>
       </c>
       <c r="B2" s="63"/>
       <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
+      <c r="D2" s="62" t="s">
+        <v>507</v>
+      </c>
       <c r="E2" s="62"/>
       <c r="F2" s="62"/>
       <c r="G2" s="62"/>
@@ -8360,7 +8379,7 @@
     </row>
     <row r="3" spans="1:14" ht="13.5" customHeight="1">
       <c r="A3" s="57" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A2:A11" si="0">IF(COUNTA($D3:$N3)=0,"","CR-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
       <c r="B3" s="63"/>
@@ -8460,7 +8479,7 @@
       </c>
       <c r="B8" s="63"/>
       <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
+      <c r="D8" s="206"/>
       <c r="E8" s="62"/>
       <c r="F8" s="62"/>
       <c r="G8" s="62"/>
@@ -18333,7 +18352,7 @@
         <f>IF($O22="","",INDEX('Project Plan'!$G$2:$G$201,MATCH($O22,'Project Plan'!$V$2:$V$201,0)))</f>
         <v/>
       </c>
-      <c r="F22" s="66" t="str">
+      <c r="F22" s="205" t="str">
         <f>IF($O22="","",INDEX('Project Plan'!$I$2:$I$201,MATCH($O22,'Project Plan'!$V$2:$V$201,0)))</f>
         <v/>
       </c>
@@ -29817,7 +29836,7 @@
       <c r="F16" s="125"/>
       <c r="G16" s="130">
         <f>MAX(COUNTIF('Change Management Plan'!$D:$D,"&lt;&gt;")-1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="125"/>
       <c r="I16" s="128">
@@ -31134,9 +31153,7 @@
         <f>IFERROR(MATCH(ROW()-1,'RAID Log'!$S:$S,0),"")</f>
         <v/>
       </c>
-      <c r="C7" s="46" t="s">
-        <v>506</v>
-      </c>
+      <c r="C7" s="46"/>
       <c r="D7" s="46" t="str">
         <f>IF($B7="","",IF(IFERROR(INDEX('RAID Log'!$1:$1048576,$B7,MATCH("Impact/Effect of the RAID",'RAID Log'!$1:$1,0)),"")="","",IFERROR(INDEX('RAID Log'!$1:$1048576,$B7,MATCH("Impact/Effect of the RAID",'RAID Log'!$1:$1,0)),"")))</f>
         <v/>
@@ -39506,7 +39523,9 @@
         <v>1</v>
       </c>
       <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
+      <c r="D2" s="62" t="s">
+        <v>506</v>
+      </c>
       <c r="E2" s="64"/>
       <c r="F2" s="63"/>
       <c r="G2" s="63"/>
